--- a/05_Figures/F05_classification/proteins/total/HR_LR/spls/c_data/results.xlsx
+++ b/05_Figures/F05_classification/proteins/total/HR_LR/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="220">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -131,21 +131,51 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">ACAA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APEH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDH2</t>
+  </si>
+  <si>
     <t xml:space="preserve">BLVRA</t>
   </si>
   <si>
     <t xml:space="preserve">CLIP1</t>
   </si>
   <si>
+    <t xml:space="preserve">EIF4A2</t>
+  </si>
+  <si>
     <t xml:space="preserve">FTH1</t>
   </si>
   <si>
+    <t xml:space="preserve">GLRX5</t>
+  </si>
+  <si>
     <t xml:space="preserve">GOT1</t>
   </si>
   <si>
+    <t xml:space="preserve">LAMTOR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMS3</t>
+  </si>
+  <si>
     <t xml:space="preserve">LMOD3</t>
   </si>
   <si>
+    <t xml:space="preserve">MGLL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS18B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAXE</t>
+  </si>
+  <si>
     <t xml:space="preserve">PALMD</t>
   </si>
   <si>
@@ -158,103 +188,88 @@
     <t xml:space="preserve">SRSF2</t>
   </si>
   <si>
-    <t xml:space="preserve">ACAA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APEH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF4A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLRX5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMTOR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMS3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGLL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAXE</t>
+    <t xml:space="preserve">EIF3C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGM5</t>
   </si>
   <si>
     <t xml:space="preserve">RPS20</t>
   </si>
   <si>
-    <t xml:space="preserve">EIF3C</t>
+    <t xml:space="preserve">COL18A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSFM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLUL</t>
   </si>
   <si>
     <t xml:space="preserve">LYPLA2</t>
   </si>
   <si>
+    <t xml:space="preserve">PPM1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTC38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRSF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RYR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHATL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2V1</t>
+  </si>
+  <si>
     <t xml:space="preserve">OXCT1</t>
   </si>
   <si>
-    <t xml:space="preserve">PGM5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSFM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLOT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHATL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TGM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2V1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRSF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS18B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RYR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL18A1</t>
+    <t xml:space="preserve">PPP1R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP1R3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLRX3</t>
   </si>
   <si>
     <t xml:space="preserve">GMPPB</t>
   </si>
   <si>
-    <t xml:space="preserve">PPM1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R2</t>
+    <t xml:space="preserve">PKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM20D2</t>
   </si>
   <si>
     <t xml:space="preserve">STOML2</t>
@@ -263,373 +278,376 @@
     <t xml:space="preserve">STUB1</t>
   </si>
   <si>
-    <t xml:space="preserve">TTC38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLRX3</t>
+    <t xml:space="preserve">ADSS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCAT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPNE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPDL</t>
   </si>
   <si>
     <t xml:space="preserve">MAN2C1</t>
   </si>
   <si>
-    <t xml:space="preserve">PKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADSS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCAT2</t>
+    <t xml:space="preserve">OGDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDLIM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGAM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGCD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VPS13C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIFM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1H</t>
   </si>
   <si>
     <t xml:space="preserve">BPNT1</t>
   </si>
   <si>
-    <t xml:space="preserve">CPNE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGDH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGCD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VPS13C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIFM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2D</t>
-  </si>
-  <si>
     <t xml:space="preserve">COX20</t>
   </si>
   <si>
+    <t xml:space="preserve">EIF5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELOB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HINT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACSIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGAM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPM1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RYR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABHD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACYP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARPC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BROX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCT6A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CES2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHCHD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHCHD7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLYBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ10A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJB4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1LI1</t>
+  </si>
+  <si>
     <t xml:space="preserve">EIF3B</t>
   </si>
   <si>
-    <t xml:space="preserve">EIF5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELOB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HINT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPDL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE3</t>
+    <t xml:space="preserve">EMC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENOPH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPHX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERI3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIGD1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-DRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KCTD12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LNPK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL47</t>
   </si>
   <si>
     <t xml:space="preserve">MRPS17</t>
   </si>
   <si>
-    <t xml:space="preserve">PACSIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGAM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPM1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RYR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM205</t>
+    <t xml:space="preserve">MRPS36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTCH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYOM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAMPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAF3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PABPC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBXIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCBD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDHB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDLIM5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGRMC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POFUT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP2R5D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3CB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSAPL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD23B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNF7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL10A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPLP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRAS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSU1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTNL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNX3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STX7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCLA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCLG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNE2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THOP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM43</t>
   </si>
   <si>
     <t xml:space="preserve">TPPP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAD10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACYP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARPC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BROX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCT6A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CES2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHCHD10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ10A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1LI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHDC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENOPH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPB41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPHX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERI3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIGD1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITGA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMNB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTCH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYOM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAMPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAF5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PABPC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PBXIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGAM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGRMC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2R5D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3CB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSAPL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTGR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD23B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL10A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPLP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RRAS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC24C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTNL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STX7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYNE2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THOP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIMM50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMX1</t>
   </si>
   <si>
     <t xml:space="preserve">TUBA3C</t>
@@ -1043,7 +1061,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1055,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.526672637512813</v>
+        <v>0.49630040275005</v>
       </c>
       <c r="K2"/>
       <c r="L2"/>
@@ -1078,10 +1096,10 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0.229166666666667</v>
@@ -1090,17 +1108,11 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.526672637512813</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.736318407960199</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.421770833333333</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.259759409277899</v>
-      </c>
+        <v>0.49630040275005</v>
+      </c>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1121,1606 +1133,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.333333333333333</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.645833333333333</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.208333333333333</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.104166666666667</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.0416666666666667</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.395833333333333</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.354166666666667</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.770833333333333</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.395833333333333</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.333333333333333</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.541666666666667</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.791666666666667</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0.666666666666667</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0.770833333333333</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0.208333333333333</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0.354166666666667</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="n">
-        <v>0.0416666666666667</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="n">
-        <v>0.0625</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="n">
-        <v>0.3125</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="n">
-        <v>0.708333333333333</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="n">
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="n">
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="n">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="n">
-        <v>0.395833333333333</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="n">
-        <v>0.354166666666667</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="n">
-        <v>0.270833333333333</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="n">
-        <v>0.729166666666667</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="n">
-        <v>0.354166666666667</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="n">
-        <v>0.0208333333333333</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="n">
-        <v>0.270833333333333</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="n">
-        <v>0.479166666666667</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="n">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="n">
-        <v>0.354166666666667</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="n">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="n">
-        <v>0.708333333333333</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="n">
-        <v>0.479166666666667</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="n">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="n">
-        <v>0.479166666666667</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="n">
-        <v>0.479166666666667</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="n">
-        <v>0.104166666666667</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="n">
-        <v>0.9375</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="n">
-        <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="n">
-        <v>0.8125</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="n">
-        <v>0.520833333333333</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="n">
-        <v>0.395833333333333</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="n">
-        <v>0.291666666666667</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="n">
-        <v>0.333333333333333</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="n">
-        <v>0.395833333333333</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="n">
-        <v>0.666666666666667</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="n">
-        <v>0.479166666666667</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="n">
-        <v>0.979166666666667</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="n">
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="n">
-        <v>0.0416666666666667</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="n">
-        <v>0.270833333333333</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="n">
-        <v>0.604166666666667</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="n">
-        <v>0.270833333333333</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="n">
-        <v>0.895833333333333</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="n">
-        <v>0.395833333333333</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="n">
-        <v>0.979166666666667</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="n">
-        <v>0.791666666666667</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="n">
-        <v>0.979166666666667</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="n">
-        <v>0.0625</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="n">
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="n">
-        <v>0.791666666666667</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="n">
-        <v>0.916666666666667</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="n">
-        <v>0.0416666666666667</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="n">
-        <v>0.729166666666667</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="n">
-        <v>0.583333333333333</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="n">
-        <v>0.333333333333333</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="n">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="n">
-        <v>0.979166666666667</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="n">
-        <v>0.354166666666667</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="n">
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="n">
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="n">
-        <v>0.0625</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="n">
-        <v>0.541666666666667</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="n">
-        <v>0.604166666666667</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="n">
-        <v>0.729166666666667</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="n">
-        <v>0.145833333333333</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="n">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="n">
-        <v>0.333333333333333</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="n">
-        <v>0.583333333333333</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="n">
-        <v>0.479166666666667</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="n">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="n">
-        <v>0.208333333333333</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="n">
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="n">
-        <v>0.354166666666667</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="n">
-        <v>0.583333333333333</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="n">
-        <v>0.208333333333333</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="n">
-        <v>0.208333333333333</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="n">
-        <v>0.458333333333333</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="n">
-        <v>0.541666666666667</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="n">
-        <v>0.291666666666667</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="n">
-        <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="n">
-        <v>0.916666666666667</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="n">
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="n">
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="n">
-        <v>0.645833333333333</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="n">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="n">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="n">
-        <v>0.354166666666667</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="n">
-        <v>0.270833333333333</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="n">
-        <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="n">
-        <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="n">
-        <v>0.541666666666667</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="n">
-        <v>0.0416666666666667</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="n">
-        <v>0.479166666666667</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="n">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="n">
-        <v>0.708333333333333</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="n">
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="n">
-        <v>0.0416666666666667</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="n">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="n">
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="n">
-        <v>0.395833333333333</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="n">
-        <v>0.666666666666667</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="n">
-        <v>0.708333333333333</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="n">
-        <v>0.291666666666667</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="n">
-        <v>0.458333333333333</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="n">
-        <v>0.3125</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="n">
-        <v>0.833333333333333</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="n">
-        <v>0.145833333333333</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="n">
-        <v>0.895833333333333</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="n">
-        <v>0.145833333333333</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="n">
-        <v>0.145833333333333</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="n">
-        <v>0.645833333333333</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="n">
-        <v>0.520833333333333</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="n">
-        <v>0.0416666666666667</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="n">
-        <v>0.958333333333333</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="n">
-        <v>0.770833333333333</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="n">
-        <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="n">
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="n">
-        <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="n">
-        <v>0.291666666666667</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="n">
-        <v>0.458333333333333</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="n">
-        <v>0.270833333333333</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -2757,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.330977200039488</v>
+        <v>0.248331429844144</v>
       </c>
     </row>
     <row r="3">
@@ -2771,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.57023740323075</v>
+        <v>0.522701149553727</v>
       </c>
     </row>
     <row r="4">
@@ -2785,7 +1197,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0578101081432126</v>
+        <v>0.278312898826569</v>
       </c>
     </row>
     <row r="5">
@@ -2799,7 +1211,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.06284764602431</v>
+        <v>-1.03206293871368</v>
       </c>
     </row>
     <row r="6">
@@ -2813,7 +1225,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.10054442904395</v>
+        <v>0.00746957954262872</v>
       </c>
     </row>
     <row r="7">
@@ -2827,7 +1239,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0351810076622283</v>
+        <v>0.0212179094007192</v>
       </c>
     </row>
     <row r="8">
@@ -2841,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.346703302088558</v>
+        <v>0.343575670948414</v>
       </c>
     </row>
     <row r="9">
@@ -2855,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.411111021900136</v>
+        <v>0.400455079889681</v>
       </c>
     </row>
     <row r="10">
@@ -2869,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.492912875660201</v>
+        <v>0.52430893700097</v>
       </c>
     </row>
     <row r="11">
@@ -2883,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.187011563299467</v>
+        <v>0.165907016942753</v>
       </c>
     </row>
     <row r="12">
@@ -2897,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.92484036657129</v>
+        <v>0.926016604226685</v>
       </c>
     </row>
     <row r="13">
@@ -2911,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.541412132418907</v>
+        <v>0.540812426855422</v>
       </c>
     </row>
     <row r="14">
@@ -2925,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.355330098156864</v>
+        <v>0.31944366608695</v>
       </c>
     </row>
     <row r="15">
@@ -2939,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0500092759657943</v>
+        <v>-0.0173890058321987</v>
       </c>
     </row>
   </sheetData>
@@ -3101,10 +1513,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="12">
@@ -3115,10 +1527,10 @@
         <v>48</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="13">
@@ -3129,10 +1541,10 @@
         <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="14">
@@ -3143,10 +1555,10 @@
         <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="15">
@@ -3157,10 +1569,10 @@
         <v>51</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="16">
@@ -3171,10 +1583,10 @@
         <v>52</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="17">
@@ -3185,10 +1597,10 @@
         <v>53</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="18">
@@ -3199,10 +1611,10 @@
         <v>54</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="19">
@@ -3213,10 +1625,10 @@
         <v>55</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="20">
@@ -3227,10 +1639,10 @@
         <v>56</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="21">
@@ -3241,10 +1653,10 @@
         <v>57</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>0.785714285714286</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="22">
@@ -3255,10 +1667,10 @@
         <v>58</v>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>0.785714285714286</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +1681,10 @@
         <v>59</v>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
-        <v>0.785714285714286</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="24">
@@ -3297,10 +1709,10 @@
         <v>61</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="26">
@@ -3311,10 +1723,10 @@
         <v>62</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="27">
@@ -3339,10 +1751,10 @@
         <v>64</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="29">
@@ -3353,10 +1765,10 @@
         <v>65</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="30">
@@ -3367,10 +1779,10 @@
         <v>66</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>0.571428571428571</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="31">
@@ -3381,10 +1793,10 @@
         <v>67</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>0.571428571428571</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="32">
@@ -3395,10 +1807,10 @@
         <v>68</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="33">
@@ -3409,10 +1821,10 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="34">
@@ -3423,10 +1835,10 @@
         <v>70</v>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="35">
@@ -3437,10 +1849,10 @@
         <v>71</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="36">
@@ -3465,10 +1877,10 @@
         <v>73</v>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>0.428571428571429</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38">
@@ -3479,10 +1891,10 @@
         <v>74</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>0.428571428571429</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
@@ -3493,10 +1905,10 @@
         <v>75</v>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>0.428571428571429</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40">
@@ -3507,10 +1919,10 @@
         <v>76</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>0.357142857142857</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="41">
@@ -3521,10 +1933,10 @@
         <v>77</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>0.357142857142857</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="42">
@@ -3577,10 +1989,10 @@
         <v>81</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="46">
@@ -3591,10 +2003,10 @@
         <v>82</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="47">
@@ -3647,10 +2059,10 @@
         <v>86</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="51">
@@ -3759,10 +2171,10 @@
         <v>94</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="59">
@@ -3773,10 +2185,10 @@
         <v>95</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="60">
@@ -3787,10 +2199,10 @@
         <v>96</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="61">
@@ -3801,10 +2213,10 @@
         <v>97</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="62">
@@ -5428,6 +3840,90 @@
         <v>1</v>
       </c>
       <c r="D177" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>214</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>215</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>216</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>217</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>218</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>219</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F05_classification/proteins/total/HR_LR/spls/c_data/results.xlsx
+++ b/05_Figures/F05_classification/proteins/total/HR_LR/spls/c_data/results.xlsx
@@ -1099,7 +1099,7 @@
         <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>0.229166666666667</v>
@@ -1110,9 +1110,15 @@
       <c r="J3" t="n">
         <v>0.49630040275005</v>
       </c>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="K3" t="n">
+        <v>0.711442786069652</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.420729166666667</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.256125213893384</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1133,6 +1139,1606 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.229166666666667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.229166666666667</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.416666666666667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.354166666666667</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.145833333333333</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.729166666666667</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.833333333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.145833333333333</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.604166666666667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.854166666666667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.833333333333333</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.916666666666667</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0.458333333333333</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0.416666666666667</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0.0208333333333333</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0.145833333333333</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0.708333333333333</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0.395833333333333</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0.520833333333333</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.395833333333333</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0.645833333333333</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0.416666666666667</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0.229166666666667</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0.583333333333333</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0.479166666666667</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0.0416666666666667</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0.520833333333333</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0.270833333333333</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0.583333333333333</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0.895833333333333</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="n">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0.395833333333333</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0.770833333333333</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0.833333333333333</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0.270833333333333</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0.229166666666667</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0.479166666666667</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0.416666666666667</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0.958333333333333</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0.354166666666667</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0.708333333333333</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0.229166666666667</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0.583333333333333</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0.979166666666667</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0.395833333333333</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="n">
+        <v>0.833333333333333</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0.791666666666667</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="n">
+        <v>0.520833333333333</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0.770833333333333</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0.916666666666667</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="n">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="n">
+        <v>0.645833333333333</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="n">
+        <v>0.416666666666667</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.979166666666667</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.354166666666667</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.604166666666667</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.645833333333333</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.145833333333333</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.520833333333333</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.979166666666667</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.145833333333333</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.229166666666667</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.145833333333333</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.520833333333333</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.479166666666667</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="n">
+        <v>0.541666666666667</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="n">
+        <v>0.270833333333333</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0.854166666666667</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0.145833333333333</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0.479166666666667</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0.708333333333333</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="n">
+        <v>0.604166666666667</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="n">
+        <v>0.583333333333333</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="n">
+        <v>0.541666666666667</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="n">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="n">
+        <v>0.479166666666667</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="n">
+        <v>0.395833333333333</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="n">
+        <v>0.0416666666666667</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0.229166666666667</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="n">
+        <v>0.604166666666667</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0.145833333333333</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0.770833333333333</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="n">
+        <v>0.479166666666667</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="n">
+        <v>0.708333333333333</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="n">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="n">
+        <v>0.458333333333333</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="n">
+        <v>0.458333333333333</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="n">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="n">
+        <v>0.854166666666667</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="n">
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="n">
+        <v>0.0416666666666667</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="n">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="n">
+        <v>0.708333333333333</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="n">
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="n">
+        <v>0.520833333333333</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
